--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.12614827758529</v>
+        <v>3.27049909510761</v>
       </c>
       <c r="D2" t="n">
-        <v>20.08946226029006</v>
+        <v>3.264537617297135</v>
       </c>
       <c r="E2" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F2" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.5101296008972</v>
+        <v>1.870396060145795</v>
       </c>
       <c r="D3" t="n">
-        <v>14.2520145235457</v>
+        <v>2.315952360076177</v>
       </c>
       <c r="E3" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F3" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4.303624801649839</v>
+        <v>0.6993390302680988</v>
       </c>
       <c r="D4" t="n">
-        <v>3.62960177217239</v>
+        <v>0.5898102879780134</v>
       </c>
       <c r="E4" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F4" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.032585106239868</v>
+        <v>0.9802950797639786</v>
       </c>
       <c r="D5" t="n">
-        <v>6.159902290769896</v>
+        <v>1.000984122250108</v>
       </c>
       <c r="E5" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F5" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.50755309140652</v>
+        <v>4.30747737735356</v>
       </c>
       <c r="D6" t="n">
-        <v>26.6403697353245</v>
+        <v>4.329060081990231</v>
       </c>
       <c r="E6" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F6" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.95087715737604</v>
+        <v>4.379517538073607</v>
       </c>
       <c r="D7" t="n">
-        <v>26.97602119487816</v>
+        <v>4.383603444167702</v>
       </c>
       <c r="E7" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F7" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.21440098238244</v>
+        <v>6.534840159637147</v>
       </c>
       <c r="D8" t="n">
-        <v>39.4308744002883</v>
+        <v>6.407517090046849</v>
       </c>
       <c r="E8" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F8" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.51050652196184</v>
+        <v>5.770457309818799</v>
       </c>
       <c r="D9" t="n">
-        <v>33.95855093756668</v>
+        <v>5.518264527354585</v>
       </c>
       <c r="E9" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F9" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.6100379958733</v>
+        <v>7.574131174329411</v>
       </c>
       <c r="D10" t="n">
-        <v>44.87399023542161</v>
+        <v>7.292023413256012</v>
       </c>
       <c r="E10" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F10" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.39921166860121</v>
+        <v>3.477371896147696</v>
       </c>
       <c r="D11" t="n">
-        <v>23.21377999347435</v>
+        <v>3.772239248939582</v>
       </c>
       <c r="E11" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F11" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>16.55294197071161</v>
+        <v>2.689853070240636</v>
       </c>
       <c r="D12" t="n">
-        <v>15.88453590789749</v>
+        <v>2.581237085033342</v>
       </c>
       <c r="E12" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F12" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.7919584626607</v>
+        <v>6.466193250182364</v>
       </c>
       <c r="D13" t="n">
-        <v>37.23859779516501</v>
+        <v>6.051272141714315</v>
       </c>
       <c r="E13" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F13" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.59883317947923</v>
+        <v>4.322310391665376</v>
       </c>
       <c r="D14" t="n">
-        <v>29.35821867310437</v>
+        <v>4.77071053437946</v>
       </c>
       <c r="E14" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F14" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>32.44272204633744</v>
+        <v>5.271942332529834</v>
       </c>
       <c r="D15" t="n">
-        <v>34.64993646479224</v>
+        <v>5.630614675528739</v>
       </c>
       <c r="E15" t="n">
-        <v>12.44544112681816</v>
+        <v>2.022384183107951</v>
       </c>
       <c r="F15" t="n">
-        <v>11.91232225185643</v>
+        <v>1.935752365926669</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
